--- a/july 2026/LMT_JULY_26/Risen/Risan Manavan.xlsx
+++ b/july 2026/LMT_JULY_26/Risen/Risan Manavan.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D7760B5-6E2D-4C71-88B7-C2259A80F8E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95CE777C-0726-49E7-9263-187236057173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1579" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1580" uniqueCount="107">
   <si>
     <t>Gm</t>
   </si>
@@ -3333,7 +3333,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -3361,7 +3361,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46201</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -4552,7 +4552,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -4580,7 +4580,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46201</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -5771,7 +5771,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -5799,7 +5799,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46201</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -6990,7 +6990,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -7018,7 +7018,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46201</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -8209,7 +8209,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -8237,7 +8237,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46201</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -9428,7 +9428,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -9456,7 +9456,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46201</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -10644,7 +10644,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -10672,7 +10672,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46201</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -11859,7 +11859,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -11887,7 +11887,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46201</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -13074,7 +13074,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -13102,7 +13102,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46201</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -14289,7 +14289,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -14317,7 +14317,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46201</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -18254,7 +18254,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -18282,7 +18282,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46201</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -19469,7 +19469,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -19497,7 +19497,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46201</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -20684,7 +20684,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -20712,7 +20712,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46201</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -21899,7 +21899,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -21927,7 +21927,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46201</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -23119,7 +23119,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -23147,7 +23147,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46201</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -23358,7 +23358,7 @@
       </c>
       <c r="U14" s="163">
         <f>+'1'!P35</f>
-        <v>26659.367770499997</v>
+        <v>25744.067839499996</v>
       </c>
       <c r="XFD14" t="s">
         <v>75</v>
@@ -23468,15 +23468,15 @@
       </c>
       <c r="N16" s="100">
         <f>+'1'!N16+'2'!N16+'4'!N16+'3'!N16+'5'!N16+'6'!N16+'7'!N16+'8'!N16+'9'!N16+'10'!N16</f>
-        <v>1260.3591000000001</v>
+        <v>1031.2029</v>
       </c>
       <c r="O16" s="100">
         <f>+'1'!O16+'2'!O16+'4'!O16+'3'!O16+'5'!O16+'6'!O16+'7'!O16+'8'!O16+'9'!O16+'10'!O16</f>
-        <v>33.372445500000005</v>
+        <v>32.226664500000005</v>
       </c>
       <c r="P16" s="104">
         <f t="shared" ref="P16:P24" si="0">M16+N16+O16</f>
-        <v>6707.8615455000008</v>
+        <v>6477.5595645000003</v>
       </c>
       <c r="Q16" s="107"/>
       <c r="T16" s="162" t="str">
@@ -23542,15 +23542,15 @@
       </c>
       <c r="N17" s="100">
         <f>+'1'!N17+'2'!N17+'4'!N17+'3'!N17+'5'!N17+'6'!N17+'7'!N17+'8'!N17+'9'!N17+'10'!N17</f>
-        <v>840.23940000000005</v>
+        <v>687.46860000000004</v>
       </c>
       <c r="O17" s="100">
         <f>+'1'!O17+'2'!O17+'4'!O17+'3'!O17+'5'!O17+'6'!O17+'7'!O17+'8'!O17+'9'!O17+'10'!O17</f>
-        <v>22.248297000000004</v>
+        <v>21.484443000000002</v>
       </c>
       <c r="P17" s="119">
         <f t="shared" si="0"/>
-        <v>4471.9076970000006</v>
+        <v>4318.3730430000005</v>
       </c>
       <c r="S17" s="64"/>
       <c r="T17" s="162" t="str">
@@ -23686,15 +23686,15 @@
       </c>
       <c r="N19" s="100">
         <f>+'1'!N19+'2'!N19+'4'!N19+'3'!N19+'5'!N19+'6'!N19+'7'!N19+'8'!N19+'9'!N19+'10'!N19</f>
-        <v>581.70111999999995</v>
+        <v>475.93727999999993</v>
       </c>
       <c r="O19" s="100">
         <f>+'1'!O19+'2'!O19+'4'!O19+'3'!O19+'5'!O19+'6'!O19+'7'!O19+'8'!O19+'9'!O19+'10'!O19</f>
-        <v>15.402585599999998</v>
+        <v>14.873766399999999</v>
       </c>
       <c r="P19" s="119">
         <f t="shared" si="0"/>
-        <v>3095.9197055999994</v>
+        <v>2989.6270463999999</v>
       </c>
       <c r="T19" s="162" t="str">
         <f>+'6'!A5</f>
@@ -23756,15 +23756,15 @@
       </c>
       <c r="N20" s="100">
         <f>+'1'!N20+'2'!N20+'4'!N20+'3'!N20+'5'!N20+'6'!N20+'7'!N20+'8'!N20+'9'!N20+'10'!N20</f>
-        <v>581.70111999999995</v>
+        <v>475.93727999999993</v>
       </c>
       <c r="O20" s="100">
         <f>+'1'!O20+'2'!O20+'4'!O20+'3'!O20+'5'!O20+'6'!O20+'7'!O20+'8'!O20+'9'!O20+'10'!O20</f>
-        <v>15.402585599999998</v>
+        <v>14.873766399999999</v>
       </c>
       <c r="P20" s="119">
         <f t="shared" si="0"/>
-        <v>3095.9197055999994</v>
+        <v>2989.6270463999999</v>
       </c>
       <c r="T20" s="162" t="str">
         <f>+'7'!A5</f>
@@ -23826,15 +23826,15 @@
       </c>
       <c r="N21" s="100">
         <f>+'1'!N21+'2'!N21+'4'!N21+'3'!N21+'5'!N21+'6'!N21+'7'!N21+'8'!N21+'9'!N21+'10'!N21</f>
-        <v>1745.1033599999998</v>
+        <v>1427.8118399999998</v>
       </c>
       <c r="O21" s="100">
         <f>+'1'!O21+'2'!O21+'4'!O21+'3'!O21+'5'!O21+'6'!O21+'7'!O21+'8'!O21+'9'!O21+'10'!O21</f>
-        <v>46.207756799999999</v>
+        <v>44.621299199999996</v>
       </c>
       <c r="P21" s="119">
         <f t="shared" si="0"/>
-        <v>9287.7591167999999</v>
+        <v>8968.8811391999989</v>
       </c>
       <c r="T21" s="162" t="str">
         <f>+'8'!A5</f>
@@ -24097,15 +24097,15 @@
       </c>
       <c r="N25" s="141">
         <f>SUM(N16:N24)</f>
-        <v>5009.1040999999996</v>
+        <v>4098.3579</v>
       </c>
       <c r="O25" s="142">
         <f>SUM(O16:O24)</f>
-        <v>132.63367049999999</v>
+        <v>128.07993949999999</v>
       </c>
       <c r="P25" s="143">
         <f>SUM(P16:P24)</f>
-        <v>26659.367770500001</v>
+        <v>25744.0678395</v>
       </c>
       <c r="T25" s="162" t="str">
         <f>+'12'!A5</f>
@@ -24235,7 +24235,7 @@
       </c>
       <c r="U30" s="164">
         <f>SUM(U14:U28)</f>
-        <v>26659.367770499997</v>
+        <v>25744.067839499996</v>
       </c>
     </row>
     <row r="31" spans="1:21 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24357,7 +24357,7 @@
       </c>
       <c r="P36" s="152">
         <f>N25</f>
-        <v>5009.1040999999996</v>
+        <v>4098.3579</v>
       </c>
     </row>
     <row r="37" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24379,7 +24379,7 @@
       <c r="O37" s="242"/>
       <c r="P37" s="152">
         <f>P35+P36</f>
-        <v>26526.734099999998</v>
+        <v>25615.987899999996</v>
       </c>
     </row>
     <row r="38" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24404,7 +24404,7 @@
       </c>
       <c r="P38" s="152">
         <f>O38*P37</f>
-        <v>663.16835249999997</v>
+        <v>640.3996975</v>
       </c>
     </row>
     <row r="39" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24414,7 +24414,7 @@
       <c r="O39" s="220"/>
       <c r="P39" s="159">
         <f>P37+P38</f>
-        <v>27189.902452499999</v>
+        <v>26256.387597499997</v>
       </c>
     </row>
     <row r="40" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24558,7 +24558,7 @@
       <c r="L3" s="201"/>
       <c r="M3" s="201"/>
       <c r="N3" s="200">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="O3" s="200"/>
       <c r="P3" s="200"/>
@@ -24586,7 +24586,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -24614,7 +24614,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46201</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -24757,11 +24757,11 @@
         <v>60</v>
       </c>
       <c r="B12" s="76" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C12" s="77" t="str">
         <f>IF($O32&gt;21.99%,"No","Yes")</f>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="F12" s="70"/>
       <c r="G12" s="71"/>
@@ -24781,7 +24781,9 @@
     </row>
     <row r="13" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="243"/>
-      <c r="B13" s="167"/>
+      <c r="B13" s="75" t="s">
+        <v>102</v>
+      </c>
       <c r="J13" s="78"/>
       <c r="K13" s="78"/>
       <c r="L13" s="79">
@@ -24868,7 +24870,7 @@
       <c r="M15" s="250"/>
       <c r="N15" s="91">
         <f>IF(B12="Registered",18%,22%)</f>
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="O15" s="92">
         <f>IF(B11="Filer",0.5%,2.5%)</f>
@@ -24930,15 +24932,15 @@
       </c>
       <c r="N16" s="105">
         <f t="shared" ref="N16:N24" si="0">(M16*$N$15)+(J16*F16)*$N$15</f>
-        <v>1260.3591000000001</v>
+        <v>1031.2029</v>
       </c>
       <c r="O16" s="106">
         <f t="shared" ref="O16:O24" si="1">(N16+M16)*$O$15</f>
-        <v>33.372445500000005</v>
+        <v>32.226664500000005</v>
       </c>
       <c r="P16" s="104">
         <f t="shared" ref="P16:P24" si="2">M16+N16+O16</f>
-        <v>6707.8615455000008</v>
+        <v>6477.5595645000003</v>
       </c>
       <c r="Q16" s="107"/>
       <c r="XFD16" t="s">
@@ -24994,15 +24996,15 @@
       </c>
       <c r="N17" s="117">
         <f t="shared" si="0"/>
-        <v>840.23940000000005</v>
+        <v>687.46860000000004</v>
       </c>
       <c r="O17" s="118">
         <f t="shared" si="1"/>
-        <v>22.248297000000004</v>
+        <v>21.484443000000002</v>
       </c>
       <c r="P17" s="119">
         <f t="shared" si="2"/>
-        <v>4471.9076970000006</v>
+        <v>4318.3730430000005</v>
       </c>
       <c r="S17" s="64"/>
       <c r="XFD17" t="s">
@@ -25114,15 +25116,15 @@
       </c>
       <c r="N19" s="117">
         <f t="shared" si="0"/>
-        <v>581.70111999999995</v>
+        <v>475.93727999999993</v>
       </c>
       <c r="O19" s="118">
         <f t="shared" si="1"/>
-        <v>15.402585599999998</v>
+        <v>14.873766399999999</v>
       </c>
       <c r="P19" s="119">
         <f t="shared" si="2"/>
-        <v>3095.9197055999994</v>
+        <v>2989.6270463999999</v>
       </c>
     </row>
     <row r="20" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -25174,15 +25176,15 @@
       </c>
       <c r="N20" s="117">
         <f t="shared" si="0"/>
-        <v>581.70111999999995</v>
+        <v>475.93727999999993</v>
       </c>
       <c r="O20" s="118">
         <f t="shared" si="1"/>
-        <v>15.402585599999998</v>
+        <v>14.873766399999999</v>
       </c>
       <c r="P20" s="119">
         <f t="shared" si="2"/>
-        <v>3095.9197055999994</v>
+        <v>2989.6270463999999</v>
       </c>
     </row>
     <row r="21" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -25234,15 +25236,15 @@
       </c>
       <c r="N21" s="117">
         <f t="shared" si="0"/>
-        <v>1745.1033599999998</v>
+        <v>1427.8118399999998</v>
       </c>
       <c r="O21" s="118">
         <f t="shared" si="1"/>
-        <v>46.207756799999999</v>
+        <v>44.621299199999996</v>
       </c>
       <c r="P21" s="119">
         <f t="shared" si="2"/>
-        <v>9287.7591167999999</v>
+        <v>8968.8811391999989</v>
       </c>
     </row>
     <row r="22" spans="1:19 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -25449,15 +25451,15 @@
       </c>
       <c r="N25" s="141">
         <f>SUM(N16:N24)</f>
-        <v>5009.1040999999996</v>
+        <v>4098.3579</v>
       </c>
       <c r="O25" s="142">
         <f>SUM(O16:O24)</f>
-        <v>132.63367049999999</v>
+        <v>128.07993949999999</v>
       </c>
       <c r="P25" s="143">
         <f>SUM(P16:P24)</f>
-        <v>26659.367770500001</v>
+        <v>25744.0678395</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -25592,11 +25594,11 @@
       </c>
       <c r="O32" s="155">
         <f>IF(B12="Registered",18%,22%)</f>
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="P32" s="152">
         <f>N25</f>
-        <v>5009.1040999999996</v>
+        <v>4098.3579</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25618,7 +25620,7 @@
       <c r="O33" s="242"/>
       <c r="P33" s="152">
         <f>P31+P32</f>
-        <v>26526.734099999998</v>
+        <v>25615.987899999996</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -25643,7 +25645,7 @@
       </c>
       <c r="P34" s="152">
         <f>O34*P33</f>
-        <v>132.63367049999999</v>
+        <v>128.07993949999999</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -25653,7 +25655,7 @@
       <c r="O35" s="220"/>
       <c r="P35" s="159">
         <f>P33+P34</f>
-        <v>26659.367770499997</v>
+        <v>25744.067839499996</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -25825,7 +25827,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -25853,7 +25855,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46201</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -27044,7 +27046,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -27072,7 +27074,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46201</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -28262,7 +28264,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -28290,7 +28292,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46201</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -29481,7 +29483,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -29509,7 +29511,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46201</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -30700,7 +30702,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -30728,7 +30730,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46201</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
